--- a/data/GreatLink/Multi-Sector Income.xlsx
+++ b/data/GreatLink/Multi-Sector Income.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid452013"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid222591"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="521">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,90 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>0.930</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>19/02/2026</t>
+  </si>
+  <si>
+    <t>0.928</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
+    <t>0.925</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>0.926</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>0.924</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>0.923</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>0.922</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>0.921</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
     <t>02/02/2026</t>
   </si>
   <si>
-    <t>0.921</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>30/01/2026</t>
   </si>
   <si>
@@ -44,9 +119,6 @@
     <t>29/01/2026</t>
   </si>
   <si>
-    <t>0.928</t>
-  </si>
-  <si>
     <t>28/01/2026</t>
   </si>
   <si>
@@ -59,9 +131,6 @@
     <t>23/01/2026</t>
   </si>
   <si>
-    <t>0.926</t>
-  </si>
-  <si>
     <t>22/01/2026</t>
   </si>
   <si>
@@ -71,9 +140,6 @@
     <t>20/01/2026</t>
   </si>
   <si>
-    <t>0.924</t>
-  </si>
-  <si>
     <t>19/01/2026</t>
   </si>
   <si>
@@ -86,9 +152,6 @@
     <t>14/01/2026</t>
   </si>
   <si>
-    <t>0.929</t>
-  </si>
-  <si>
     <t>13/01/2026</t>
   </si>
   <si>
@@ -101,9 +164,6 @@
     <t>08/01/2026</t>
   </si>
   <si>
-    <t>0.925</t>
-  </si>
-  <si>
     <t>07/01/2026</t>
   </si>
   <si>
@@ -122,9 +182,6 @@
     <t>30/12/2025</t>
   </si>
   <si>
-    <t>0.930</t>
-  </si>
-  <si>
     <t>29/12/2025</t>
   </si>
   <si>
@@ -533,9 +590,6 @@
     <t>07/07/2025</t>
   </si>
   <si>
-    <t>0.923</t>
-  </si>
-  <si>
     <t>04/07/2025</t>
   </si>
   <si>
@@ -567,9 +621,6 @@
   </si>
   <si>
     <t>20/06/2025</t>
-  </si>
-  <si>
-    <t>0.922</t>
   </si>
   <si>
     <t>19/06/2025</t>
@@ -1879,7 +1930,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -1887,10 +1938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -1898,10 +1949,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -1909,10 +1960,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1920,10 +1971,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -1931,10 +1982,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -1942,10 +1993,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -1953,10 +2004,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -1964,10 +2015,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -1975,10 +2026,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -1986,10 +2037,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -2000,7 +2051,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -2008,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2019,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -2030,10 +2081,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -2041,10 +2092,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -2052,7 +2103,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -2063,10 +2114,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -2074,10 +2125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -2085,10 +2136,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -2096,10 +2147,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
         <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -2107,10 +2158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -2118,10 +2169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -2129,10 +2180,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -2140,10 +2191,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -2151,10 +2202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -2162,10 +2213,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -2173,10 +2224,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -2184,10 +2235,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -2195,10 +2246,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -2206,10 +2257,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -2217,10 +2268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -2228,10 +2279,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -2239,10 +2290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -2250,10 +2301,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -2261,10 +2312,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -2272,10 +2323,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -2283,10 +2334,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -2294,10 +2345,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -2305,10 +2356,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -2316,10 +2367,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -2327,10 +2378,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -2338,10 +2389,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -2349,10 +2400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -2360,10 +2411,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -2371,10 +2422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -2382,10 +2433,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -2396,7 +2447,7 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -2404,10 +2455,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -2415,10 +2466,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -2426,10 +2477,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -2437,10 +2488,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -2448,10 +2499,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -2459,10 +2510,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -2470,10 +2521,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -2481,10 +2532,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -2492,10 +2543,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -2503,10 +2554,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -2514,10 +2565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -2525,10 +2576,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -2536,10 +2587,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -2547,10 +2598,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" t="s">
         <v>77</v>
-      </c>
-      <c r="B64" t="s">
-        <v>63</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -2561,7 +2612,7 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -2572,7 +2623,7 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -2580,10 +2631,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -2591,10 +2642,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -2602,10 +2653,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -2616,7 +2667,7 @@
         <v>85</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -2624,10 +2675,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -2635,10 +2686,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -2646,10 +2697,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -2657,7 +2708,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B74" t="s">
         <v>82</v>
@@ -2668,10 +2719,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -2679,10 +2730,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -2690,10 +2741,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B77" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -2701,10 +2752,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -2712,10 +2763,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B79" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -2723,10 +2774,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -2734,10 +2785,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -2745,10 +2796,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -2756,10 +2807,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -2767,10 +2818,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -2778,10 +2829,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -2789,10 +2840,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -2800,10 +2851,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -2811,10 +2862,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>106</v>
+      </c>
+      <c r="B88" t="s">
         <v>107</v>
-      </c>
-      <c r="B88" t="s">
-        <v>97</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -2825,7 +2876,7 @@
         <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -2836,7 +2887,7 @@
         <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -2847,7 +2898,7 @@
         <v>110</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -2858,7 +2909,7 @@
         <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -2866,10 +2917,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" t="s">
         <v>112</v>
-      </c>
-      <c r="B93" t="s">
-        <v>58</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -2877,10 +2928,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
@@ -2888,10 +2939,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
@@ -2899,10 +2950,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B96" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
@@ -2910,10 +2961,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
@@ -2921,10 +2972,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="C98" t="s">
         <v>5</v>
@@ -2932,10 +2983,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
@@ -2943,10 +2994,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B100" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -2954,10 +3005,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
         <v>5</v>
@@ -2965,10 +3016,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
@@ -2976,10 +3027,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="C103" t="s">
         <v>5</v>
@@ -2987,10 +3038,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B104" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -2998,10 +3049,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -3009,10 +3060,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B106" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="C106" t="s">
         <v>5</v>
@@ -3020,10 +3071,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
@@ -3031,10 +3082,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C108" t="s">
         <v>5</v>
@@ -3042,10 +3093,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B109" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -3053,10 +3104,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C110" t="s">
         <v>5</v>
@@ -3064,10 +3115,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B111" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -3075,10 +3126,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C112" t="s">
         <v>5</v>
@@ -3086,10 +3137,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B113" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C113" t="s">
         <v>5</v>
@@ -3097,10 +3148,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="C114" t="s">
         <v>5</v>
@@ -3108,10 +3159,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B115" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
         <v>5</v>
@@ -3119,10 +3170,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="C116" t="s">
         <v>5</v>
@@ -3130,10 +3181,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
@@ -3141,10 +3192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B118" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="C118" t="s">
         <v>5</v>
@@ -3152,10 +3203,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
@@ -3163,10 +3214,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
@@ -3174,10 +3225,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B121" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
@@ -3185,10 +3236,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B122" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3196,10 +3247,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C123" t="s">
         <v>5</v>
@@ -3207,10 +3258,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -3218,10 +3269,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B125" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C125" t="s">
         <v>5</v>
@@ -3229,10 +3280,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
@@ -3240,10 +3291,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
@@ -3251,10 +3302,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="C128" t="s">
         <v>5</v>
@@ -3262,10 +3313,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
@@ -3273,10 +3324,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="C130" t="s">
         <v>5</v>
@@ -3284,10 +3335,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B131" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C131" t="s">
         <v>5</v>
@@ -3295,10 +3346,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C132" t="s">
         <v>5</v>
@@ -3306,10 +3357,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B133" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -3317,10 +3368,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
@@ -3328,10 +3379,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B135" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
@@ -3339,10 +3390,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -3350,10 +3401,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B137" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
@@ -3361,10 +3412,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
@@ -3372,10 +3423,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
@@ -3383,10 +3434,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B140" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
@@ -3394,10 +3445,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B141" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
@@ -3405,10 +3456,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B142" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -3416,10 +3467,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B143" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -3430,7 +3481,7 @@
         <v>166</v>
       </c>
       <c r="B144" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -3441,7 +3492,7 @@
         <v>167</v>
       </c>
       <c r="B145" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -3452,7 +3503,7 @@
         <v>168</v>
       </c>
       <c r="B146" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
@@ -3463,7 +3514,7 @@
         <v>169</v>
       </c>
       <c r="B147" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
@@ -3474,7 +3525,7 @@
         <v>170</v>
       </c>
       <c r="B148" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
@@ -3485,7 +3536,7 @@
         <v>171</v>
       </c>
       <c r="B149" t="s">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
@@ -3493,10 +3544,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B150" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
@@ -3504,10 +3555,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B151" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
@@ -3515,10 +3566,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B152" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C152" t="s">
         <v>5</v>
@@ -3526,10 +3577,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C153" t="s">
         <v>5</v>
@@ -3537,10 +3588,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B154" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C154" t="s">
         <v>5</v>
@@ -3548,10 +3599,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B155" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -3559,10 +3610,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B156" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="C156" t="s">
         <v>5</v>
@@ -3570,10 +3621,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B157" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C157" t="s">
         <v>5</v>
@@ -3581,10 +3632,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
+        <v>180</v>
+      </c>
+      <c r="B158" t="s">
         <v>181</v>
-      </c>
-      <c r="B158" t="s">
-        <v>9</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -3595,7 +3646,7 @@
         <v>182</v>
       </c>
       <c r="B159" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
@@ -3617,7 +3668,7 @@
         <v>185</v>
       </c>
       <c r="B161" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
@@ -3628,7 +3679,7 @@
         <v>186</v>
       </c>
       <c r="B162" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="C162" t="s">
         <v>5</v>
@@ -3639,7 +3690,7 @@
         <v>187</v>
       </c>
       <c r="B163" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C163" t="s">
         <v>5</v>
@@ -3650,7 +3701,7 @@
         <v>188</v>
       </c>
       <c r="B164" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C164" t="s">
         <v>5</v>
@@ -3661,7 +3712,7 @@
         <v>189</v>
       </c>
       <c r="B165" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C165" t="s">
         <v>5</v>
@@ -3672,7 +3723,7 @@
         <v>190</v>
       </c>
       <c r="B166" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C166" t="s">
         <v>5</v>
@@ -3683,7 +3734,7 @@
         <v>191</v>
       </c>
       <c r="B167" t="s">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
@@ -3694,7 +3745,7 @@
         <v>192</v>
       </c>
       <c r="B168" t="s">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -3705,7 +3756,7 @@
         <v>193</v>
       </c>
       <c r="B169" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -3713,10 +3764,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B170" t="s">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -3724,10 +3775,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B171" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -3735,7 +3786,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B172" t="s">
         <v>4</v>
@@ -3746,10 +3797,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B173" t="s">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -3757,10 +3808,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B174" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -3768,10 +3819,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B175" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
@@ -3779,10 +3830,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B176" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -3790,10 +3841,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B177" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
@@ -3801,10 +3852,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B178" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
@@ -3812,10 +3863,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B179" t="s">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
@@ -3823,10 +3874,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B180" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
@@ -3834,10 +3885,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B181" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -3845,10 +3896,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B182" t="s">
-        <v>212</v>
+        <v>28</v>
       </c>
       <c r="C182" t="s">
         <v>5</v>
@@ -3856,10 +3907,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B183" t="s">
-        <v>194</v>
+        <v>18</v>
       </c>
       <c r="C183" t="s">
         <v>5</v>
@@ -3867,10 +3918,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B184" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="C184" t="s">
         <v>5</v>
@@ -3878,10 +3929,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B185" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="C185" t="s">
         <v>5</v>
@@ -3889,10 +3940,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B186" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -3900,10 +3951,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B187" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
@@ -3911,10 +3962,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B188" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -3922,10 +3973,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B189" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
@@ -3933,10 +3984,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B190" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -3944,10 +3995,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B191" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -3955,10 +4006,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B192" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -3966,10 +4017,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B193" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -3977,10 +4028,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B194" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -3988,10 +4039,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B195" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -3999,10 +4050,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B196" t="s">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -4010,10 +4061,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B197" t="s">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="C197" t="s">
         <v>5</v>
@@ -4021,10 +4072,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B198" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
@@ -4032,10 +4083,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>228</v>
+      </c>
+      <c r="B199" t="s">
         <v>229</v>
-      </c>
-      <c r="B199" t="s">
-        <v>28</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
@@ -4046,7 +4097,7 @@
         <v>230</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
@@ -4057,7 +4108,7 @@
         <v>231</v>
       </c>
       <c r="B201" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
@@ -4068,7 +4119,7 @@
         <v>232</v>
       </c>
       <c r="B202" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="C202" t="s">
         <v>5</v>
@@ -4076,10 +4127,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B203" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -4087,10 +4138,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B204" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="C204" t="s">
         <v>5</v>
@@ -4098,10 +4149,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B205" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -4109,10 +4160,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B206" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
@@ -4120,10 +4171,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B207" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -4131,10 +4182,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B208" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
@@ -4142,10 +4193,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B209" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
@@ -4153,10 +4204,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B210" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
@@ -4164,10 +4215,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B211" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -4175,10 +4226,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B212" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -4186,10 +4237,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B213" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -4197,10 +4248,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B214" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
@@ -4208,10 +4259,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B215" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
@@ -4219,10 +4270,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B216" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
@@ -4230,10 +4281,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B217" t="s">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -4241,10 +4292,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B218" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="C218" t="s">
         <v>5</v>
@@ -4252,10 +4303,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B219" t="s">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -4263,10 +4314,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B220" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="C220" t="s">
         <v>5</v>
@@ -4274,10 +4325,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B221" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -4285,10 +4336,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B222" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="C222" t="s">
         <v>5</v>
@@ -4296,10 +4347,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B223" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="C223" t="s">
         <v>5</v>
@@ -4307,10 +4358,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B224" t="s">
-        <v>118</v>
+        <v>256</v>
       </c>
       <c r="C224" t="s">
         <v>5</v>
@@ -4318,10 +4369,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
+        <v>257</v>
+      </c>
+      <c r="B225" t="s">
         <v>258</v>
-      </c>
-      <c r="B225" t="s">
-        <v>93</v>
       </c>
       <c r="C225" t="s">
         <v>5</v>
@@ -4332,7 +4383,7 @@
         <v>259</v>
       </c>
       <c r="B226" t="s">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c r="C226" t="s">
         <v>5</v>
@@ -4343,7 +4394,7 @@
         <v>260</v>
       </c>
       <c r="B227" t="s">
-        <v>58</v>
+        <v>250</v>
       </c>
       <c r="C227" t="s">
         <v>5</v>
@@ -4354,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="B228" t="s">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -4365,7 +4416,7 @@
         <v>262</v>
       </c>
       <c r="B229" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -4376,7 +4427,7 @@
         <v>263</v>
       </c>
       <c r="B230" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -4387,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="B231" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C231" t="s">
         <v>5</v>
@@ -4398,7 +4449,7 @@
         <v>265</v>
       </c>
       <c r="B232" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C232" t="s">
         <v>5</v>
@@ -4409,7 +4460,7 @@
         <v>266</v>
       </c>
       <c r="B233" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C233" t="s">
         <v>5</v>
@@ -4420,7 +4471,7 @@
         <v>267</v>
       </c>
       <c r="B234" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="C234" t="s">
         <v>5</v>
@@ -4431,7 +4482,7 @@
         <v>268</v>
       </c>
       <c r="B235" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C235" t="s">
         <v>5</v>
@@ -4442,7 +4493,7 @@
         <v>269</v>
       </c>
       <c r="B236" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C236" t="s">
         <v>5</v>
@@ -4453,7 +4504,7 @@
         <v>270</v>
       </c>
       <c r="B237" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C237" t="s">
         <v>5</v>
@@ -4464,7 +4515,7 @@
         <v>271</v>
       </c>
       <c r="B238" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
@@ -4475,7 +4526,7 @@
         <v>272</v>
       </c>
       <c r="B239" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -4486,7 +4537,7 @@
         <v>273</v>
       </c>
       <c r="B240" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -4497,7 +4548,7 @@
         <v>274</v>
       </c>
       <c r="B241" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C241" t="s">
         <v>5</v>
@@ -4508,7 +4559,7 @@
         <v>275</v>
       </c>
       <c r="B242" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C242" t="s">
         <v>5</v>
@@ -4519,7 +4570,7 @@
         <v>276</v>
       </c>
       <c r="B243" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C243" t="s">
         <v>5</v>
@@ -4530,7 +4581,7 @@
         <v>277</v>
       </c>
       <c r="B244" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
@@ -4541,7 +4592,7 @@
         <v>278</v>
       </c>
       <c r="B245" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C245" t="s">
         <v>5</v>
@@ -4552,7 +4603,7 @@
         <v>279</v>
       </c>
       <c r="B246" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C246" t="s">
         <v>5</v>
@@ -4563,7 +4614,7 @@
         <v>280</v>
       </c>
       <c r="B247" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C247" t="s">
         <v>5</v>
@@ -4574,7 +4625,7 @@
         <v>281</v>
       </c>
       <c r="B248" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="C248" t="s">
         <v>5</v>
@@ -4585,7 +4636,7 @@
         <v>282</v>
       </c>
       <c r="B249" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
@@ -4596,7 +4647,7 @@
         <v>283</v>
       </c>
       <c r="B250" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
@@ -4607,7 +4658,7 @@
         <v>284</v>
       </c>
       <c r="B251" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C251" t="s">
         <v>5</v>
@@ -4618,7 +4669,7 @@
         <v>285</v>
       </c>
       <c r="B252" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C252" t="s">
         <v>5</v>
@@ -4629,7 +4680,7 @@
         <v>286</v>
       </c>
       <c r="B253" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
@@ -4640,7 +4691,7 @@
         <v>287</v>
       </c>
       <c r="B254" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="C254" t="s">
         <v>5</v>
@@ -4651,7 +4702,7 @@
         <v>288</v>
       </c>
       <c r="B255" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C255" t="s">
         <v>5</v>
@@ -4662,7 +4713,7 @@
         <v>289</v>
       </c>
       <c r="B256" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="C256" t="s">
         <v>5</v>
@@ -4673,7 +4724,7 @@
         <v>290</v>
       </c>
       <c r="B257" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -4684,7 +4735,7 @@
         <v>291</v>
       </c>
       <c r="B258" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
@@ -4695,7 +4746,7 @@
         <v>292</v>
       </c>
       <c r="B259" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C259" t="s">
         <v>5</v>
@@ -4706,7 +4757,7 @@
         <v>293</v>
       </c>
       <c r="B260" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="C260" t="s">
         <v>5</v>
@@ -4717,7 +4768,7 @@
         <v>294</v>
       </c>
       <c r="B261" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="C261" t="s">
         <v>5</v>
@@ -4728,7 +4779,7 @@
         <v>295</v>
       </c>
       <c r="B262" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
@@ -4739,7 +4790,7 @@
         <v>296</v>
       </c>
       <c r="B263" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C263" t="s">
         <v>5</v>
@@ -4750,7 +4801,7 @@
         <v>297</v>
       </c>
       <c r="B264" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
@@ -4761,7 +4812,7 @@
         <v>298</v>
       </c>
       <c r="B265" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C265" t="s">
         <v>5</v>
@@ -4772,7 +4823,7 @@
         <v>299</v>
       </c>
       <c r="B266" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="C266" t="s">
         <v>5</v>
@@ -4783,7 +4834,7 @@
         <v>300</v>
       </c>
       <c r="B267" t="s">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="C267" t="s">
         <v>5</v>
@@ -4794,7 +4845,7 @@
         <v>301</v>
       </c>
       <c r="B268" t="s">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="C268" t="s">
         <v>5</v>
@@ -4805,7 +4856,7 @@
         <v>302</v>
       </c>
       <c r="B269" t="s">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
@@ -4816,7 +4867,7 @@
         <v>303</v>
       </c>
       <c r="B270" t="s">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="C270" t="s">
         <v>5</v>
@@ -4827,7 +4878,7 @@
         <v>304</v>
       </c>
       <c r="B271" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="C271" t="s">
         <v>5</v>
@@ -4838,7 +4889,7 @@
         <v>305</v>
       </c>
       <c r="B272" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -4849,7 +4900,7 @@
         <v>306</v>
       </c>
       <c r="B273" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C273" t="s">
         <v>5</v>
@@ -4860,7 +4911,7 @@
         <v>307</v>
       </c>
       <c r="B274" t="s">
-        <v>172</v>
+        <v>4</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -4871,7 +4922,7 @@
         <v>308</v>
       </c>
       <c r="B275" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -4882,7 +4933,7 @@
         <v>309</v>
       </c>
       <c r="B276" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -4893,7 +4944,7 @@
         <v>310</v>
       </c>
       <c r="B277" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -4904,7 +4955,7 @@
         <v>311</v>
       </c>
       <c r="B278" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -4915,7 +4966,7 @@
         <v>312</v>
       </c>
       <c r="B279" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C279" t="s">
         <v>5</v>
@@ -4926,7 +4977,7 @@
         <v>313</v>
       </c>
       <c r="B280" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -4937,7 +4988,7 @@
         <v>314</v>
       </c>
       <c r="B281" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C281" t="s">
         <v>5</v>
@@ -4948,7 +4999,7 @@
         <v>315</v>
       </c>
       <c r="B282" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C282" t="s">
         <v>5</v>
@@ -4959,7 +5010,7 @@
         <v>316</v>
       </c>
       <c r="B283" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C283" t="s">
         <v>5</v>
@@ -4970,7 +5021,7 @@
         <v>317</v>
       </c>
       <c r="B284" t="s">
-        <v>9</v>
+        <v>219</v>
       </c>
       <c r="C284" t="s">
         <v>5</v>
@@ -4981,7 +5032,7 @@
         <v>318</v>
       </c>
       <c r="B285" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="C285" t="s">
         <v>5</v>
@@ -4992,7 +5043,7 @@
         <v>319</v>
       </c>
       <c r="B286" t="s">
-        <v>61</v>
+        <v>219</v>
       </c>
       <c r="C286" t="s">
         <v>5</v>
@@ -5003,7 +5054,7 @@
         <v>320</v>
       </c>
       <c r="B287" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C287" t="s">
         <v>5</v>
@@ -5014,7 +5065,7 @@
         <v>321</v>
       </c>
       <c r="B288" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="C288" t="s">
         <v>5</v>
@@ -5025,7 +5076,7 @@
         <v>322</v>
       </c>
       <c r="B289" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="C289" t="s">
         <v>5</v>
@@ -5036,7 +5087,7 @@
         <v>323</v>
       </c>
       <c r="B290" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -5047,7 +5098,7 @@
         <v>324</v>
       </c>
       <c r="B291" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="C291" t="s">
         <v>5</v>
@@ -5058,7 +5109,7 @@
         <v>325</v>
       </c>
       <c r="B292" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="C292" t="s">
         <v>5</v>
@@ -5069,7 +5120,7 @@
         <v>326</v>
       </c>
       <c r="B293" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C293" t="s">
         <v>5</v>
@@ -5080,7 +5131,7 @@
         <v>327</v>
       </c>
       <c r="B294" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
         <v>5</v>
@@ -5091,7 +5142,7 @@
         <v>328</v>
       </c>
       <c r="B295" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C295" t="s">
         <v>5</v>
@@ -5102,7 +5153,7 @@
         <v>329</v>
       </c>
       <c r="B296" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="C296" t="s">
         <v>5</v>
@@ -5113,7 +5164,7 @@
         <v>330</v>
       </c>
       <c r="B297" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="C297" t="s">
         <v>5</v>
@@ -5124,7 +5175,7 @@
         <v>331</v>
       </c>
       <c r="B298" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="C298" t="s">
         <v>5</v>
@@ -5135,7 +5186,7 @@
         <v>332</v>
       </c>
       <c r="B299" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -5146,7 +5197,7 @@
         <v>333</v>
       </c>
       <c r="B300" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="C300" t="s">
         <v>5</v>
@@ -5157,7 +5208,7 @@
         <v>334</v>
       </c>
       <c r="B301" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
         <v>5</v>
@@ -5168,7 +5219,7 @@
         <v>335</v>
       </c>
       <c r="B302" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="C302" t="s">
         <v>5</v>
@@ -5179,7 +5230,7 @@
         <v>336</v>
       </c>
       <c r="B303" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C303" t="s">
         <v>5</v>
@@ -5190,7 +5241,7 @@
         <v>337</v>
       </c>
       <c r="B304" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C304" t="s">
         <v>5</v>
@@ -5201,7 +5252,7 @@
         <v>338</v>
       </c>
       <c r="B305" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="C305" t="s">
         <v>5</v>
@@ -5212,7 +5263,7 @@
         <v>339</v>
       </c>
       <c r="B306" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="C306" t="s">
         <v>5</v>
@@ -5223,7 +5274,7 @@
         <v>340</v>
       </c>
       <c r="B307" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C307" t="s">
         <v>5</v>
@@ -5234,7 +5285,7 @@
         <v>341</v>
       </c>
       <c r="B308" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C308" t="s">
         <v>5</v>
@@ -5245,7 +5296,7 @@
         <v>342</v>
       </c>
       <c r="B309" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C309" t="s">
         <v>5</v>
@@ -5256,7 +5307,7 @@
         <v>343</v>
       </c>
       <c r="B310" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C310" t="s">
         <v>5</v>
@@ -5267,7 +5318,7 @@
         <v>344</v>
       </c>
       <c r="B311" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C311" t="s">
         <v>5</v>
@@ -5278,7 +5329,7 @@
         <v>345</v>
       </c>
       <c r="B312" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C312" t="s">
         <v>5</v>
@@ -5289,7 +5340,7 @@
         <v>346</v>
       </c>
       <c r="B313" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C313" t="s">
         <v>5</v>
@@ -5300,7 +5351,7 @@
         <v>347</v>
       </c>
       <c r="B314" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C314" t="s">
         <v>5</v>
@@ -5311,7 +5362,7 @@
         <v>348</v>
       </c>
       <c r="B315" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C315" t="s">
         <v>5</v>
@@ -5322,7 +5373,7 @@
         <v>349</v>
       </c>
       <c r="B316" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="C316" t="s">
         <v>5</v>
@@ -5333,7 +5384,7 @@
         <v>350</v>
       </c>
       <c r="B317" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="C317" t="s">
         <v>5</v>
@@ -5344,7 +5395,7 @@
         <v>351</v>
       </c>
       <c r="B318" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C318" t="s">
         <v>5</v>
@@ -5355,7 +5406,7 @@
         <v>352</v>
       </c>
       <c r="B319" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C319" t="s">
         <v>5</v>
@@ -5366,7 +5417,7 @@
         <v>353</v>
       </c>
       <c r="B320" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="C320" t="s">
         <v>5</v>
@@ -5377,7 +5428,7 @@
         <v>354</v>
       </c>
       <c r="B321" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C321" t="s">
         <v>5</v>
@@ -5388,7 +5439,7 @@
         <v>355</v>
       </c>
       <c r="B322" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C322" t="s">
         <v>5</v>
@@ -5399,7 +5450,7 @@
         <v>356</v>
       </c>
       <c r="B323" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C323" t="s">
         <v>5</v>
@@ -5410,7 +5461,7 @@
         <v>357</v>
       </c>
       <c r="B324" t="s">
-        <v>358</v>
+        <v>116</v>
       </c>
       <c r="C324" t="s">
         <v>5</v>
@@ -5418,10 +5469,10 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B325" t="s">
-        <v>360</v>
+        <v>116</v>
       </c>
       <c r="C325" t="s">
         <v>5</v>
@@ -5429,10 +5480,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B326" t="s">
-        <v>362</v>
+        <v>116</v>
       </c>
       <c r="C326" t="s">
         <v>5</v>
@@ -5440,10 +5491,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B327" t="s">
-        <v>364</v>
+        <v>116</v>
       </c>
       <c r="C327" t="s">
         <v>5</v>
@@ -5451,10 +5502,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B328" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="C328" t="s">
         <v>5</v>
@@ -5462,10 +5513,10 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B329" t="s">
-        <v>362</v>
+        <v>107</v>
       </c>
       <c r="C329" t="s">
         <v>5</v>
@@ -5473,10 +5524,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B330" t="s">
-        <v>364</v>
+        <v>101</v>
       </c>
       <c r="C330" t="s">
         <v>5</v>
@@ -5484,10 +5535,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B331" t="s">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="C331" t="s">
         <v>5</v>
@@ -5495,10 +5546,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B332" t="s">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="C332" t="s">
         <v>5</v>
@@ -5506,10 +5557,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B333" t="s">
-        <v>364</v>
+        <v>4</v>
       </c>
       <c r="C333" t="s">
         <v>5</v>
@@ -5517,10 +5568,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B334" t="s">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="C334" t="s">
         <v>5</v>
@@ -5528,10 +5579,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B335" t="s">
-        <v>364</v>
+        <v>137</v>
       </c>
       <c r="C335" t="s">
         <v>5</v>
@@ -5539,10 +5590,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B336" t="s">
-        <v>362</v>
+        <v>107</v>
       </c>
       <c r="C336" t="s">
         <v>5</v>
@@ -5550,10 +5601,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B337" t="s">
-        <v>376</v>
+        <v>101</v>
       </c>
       <c r="C337" t="s">
         <v>5</v>
@@ -5561,10 +5612,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B338" t="s">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="C338" t="s">
         <v>5</v>
@@ -5572,10 +5623,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B339" t="s">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="C339" t="s">
         <v>5</v>
@@ -5583,10 +5634,10 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B340" t="s">
-        <v>381</v>
+        <v>107</v>
       </c>
       <c r="C340" t="s">
         <v>5</v>
@@ -5594,10 +5645,10 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B341" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C341" t="s">
         <v>5</v>
@@ -5605,10 +5656,10 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B342" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C342" t="s">
         <v>5</v>
@@ -5616,10 +5667,10 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B343" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C343" t="s">
         <v>5</v>
@@ -5627,10 +5678,10 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B344" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C344" t="s">
         <v>5</v>
@@ -5638,7 +5689,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B345" t="s">
         <v>383</v>
@@ -5649,10 +5700,10 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B346" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C346" t="s">
         <v>5</v>
@@ -5660,10 +5711,10 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B347" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C347" t="s">
         <v>5</v>
@@ -5671,10 +5722,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B348" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C348" t="s">
         <v>5</v>
@@ -5682,10 +5733,10 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B349" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C349" t="s">
         <v>5</v>
@@ -5693,10 +5744,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B350" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C350" t="s">
         <v>5</v>
@@ -5704,7 +5755,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B351" t="s">
         <v>381</v>
@@ -5715,10 +5766,10 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B352" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C352" t="s">
         <v>5</v>
@@ -5726,10 +5777,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B353" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C353" t="s">
         <v>5</v>
@@ -5737,10 +5788,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B354" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C354" t="s">
         <v>5</v>
@@ -5748,10 +5799,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B355" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="C355" t="s">
         <v>5</v>
@@ -5759,10 +5810,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B356" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C356" t="s">
         <v>5</v>
@@ -5770,10 +5821,10 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B357" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C357" t="s">
         <v>5</v>
@@ -5781,10 +5832,10 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B358" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -5792,10 +5843,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B359" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C359" t="s">
         <v>5</v>
@@ -5803,10 +5854,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B360" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="C360" t="s">
         <v>5</v>
@@ -5814,10 +5865,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B361" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C361" t="s">
         <v>5</v>
@@ -5825,10 +5876,10 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B362" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C362" t="s">
         <v>5</v>
@@ -5836,10 +5887,10 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B363" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
@@ -5847,10 +5898,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B364" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C364" t="s">
         <v>5</v>
@@ -5858,10 +5909,10 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B365" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C365" t="s">
         <v>5</v>
@@ -5869,10 +5920,10 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B366" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C366" t="s">
         <v>5</v>
@@ -5880,10 +5931,10 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B367" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C367" t="s">
         <v>5</v>
@@ -5891,10 +5942,10 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B368" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="C368" t="s">
         <v>5</v>
@@ -5902,10 +5953,10 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B369" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C369" t="s">
         <v>5</v>
@@ -5913,10 +5964,10 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B370" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C370" t="s">
         <v>5</v>
@@ -5924,10 +5975,10 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B371" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C371" t="s">
         <v>5</v>
@@ -5935,10 +5986,10 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B372" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C372" t="s">
         <v>5</v>
@@ -5946,10 +5997,10 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B373" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="C373" t="s">
         <v>5</v>
@@ -5957,10 +6008,10 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B374" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="C374" t="s">
         <v>5</v>
@@ -5968,10 +6019,10 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B375" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C375" t="s">
         <v>5</v>
@@ -5979,10 +6030,10 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B376" t="s">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="C376" t="s">
         <v>5</v>
@@ -5990,10 +6041,10 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B377" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C377" t="s">
         <v>5</v>
@@ -6001,10 +6052,10 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B378" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="C378" t="s">
         <v>5</v>
@@ -6012,10 +6063,10 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B379" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="C379" t="s">
         <v>5</v>
@@ -6023,10 +6074,10 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B380" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="C380" t="s">
         <v>5</v>
@@ -6034,10 +6085,10 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
+        <v>430</v>
+      </c>
+      <c r="B381" t="s">
         <v>431</v>
-      </c>
-      <c r="B381" t="s">
-        <v>432</v>
       </c>
       <c r="C381" t="s">
         <v>5</v>
@@ -6045,10 +6096,10 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B382" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="C382" t="s">
         <v>5</v>
@@ -6056,10 +6107,10 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B383" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C383" t="s">
         <v>5</v>
@@ -6067,10 +6118,10 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B384" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C384" t="s">
         <v>5</v>
@@ -6078,10 +6129,10 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B385" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="C385" t="s">
         <v>5</v>
@@ -6089,10 +6140,10 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B386" t="s">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
@@ -6100,10 +6151,10 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B387" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="C387" t="s">
         <v>5</v>
@@ -6111,10 +6162,10 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B388" t="s">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="C388" t="s">
         <v>5</v>
@@ -6122,10 +6173,10 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B389" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="C389" t="s">
         <v>5</v>
@@ -6133,10 +6184,10 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B390" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
@@ -6144,10 +6195,10 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B391" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C391" t="s">
         <v>5</v>
@@ -6155,10 +6206,10 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B392" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C392" t="s">
         <v>5</v>
@@ -6166,10 +6217,10 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B393" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="C393" t="s">
         <v>5</v>
@@ -6177,10 +6228,10 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B394" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="C394" t="s">
         <v>5</v>
@@ -6188,10 +6239,10 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B395" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="C395" t="s">
         <v>5</v>
@@ -6199,10 +6250,10 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B396" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C396" t="s">
         <v>5</v>
@@ -6210,10 +6261,10 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B397" t="s">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="C397" t="s">
         <v>5</v>
@@ -6221,10 +6272,10 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B398" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C398" t="s">
         <v>5</v>
@@ -6232,10 +6283,10 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B399" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="C399" t="s">
         <v>5</v>
@@ -6243,10 +6294,10 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B400" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="C400" t="s">
         <v>5</v>
@@ -6254,10 +6305,10 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B401" t="s">
-        <v>88</v>
+        <v>449</v>
       </c>
       <c r="C401" t="s">
         <v>5</v>
@@ -6265,10 +6316,10 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B402" t="s">
-        <v>88</v>
+        <v>449</v>
       </c>
       <c r="C402" t="s">
         <v>5</v>
@@ -6276,10 +6327,10 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B403" t="s">
-        <v>93</v>
+        <v>383</v>
       </c>
       <c r="C403" t="s">
         <v>5</v>
@@ -6287,10 +6338,10 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B404" t="s">
-        <v>58</v>
+        <v>379</v>
       </c>
       <c r="C404" t="s">
         <v>5</v>
@@ -6298,10 +6349,10 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B405" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C405" t="s">
         <v>5</v>
@@ -6309,10 +6360,10 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B406" t="s">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="C406" t="s">
         <v>5</v>
@@ -6320,10 +6371,10 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B407" t="s">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="C407" t="s">
         <v>5</v>
@@ -6331,10 +6382,10 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B408" t="s">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="C408" t="s">
         <v>5</v>
@@ -6342,10 +6393,10 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B409" t="s">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="C409" t="s">
         <v>5</v>
@@ -6353,10 +6404,10 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B410" t="s">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="C410" t="s">
         <v>5</v>
@@ -6364,10 +6415,10 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B411" t="s">
-        <v>364</v>
+        <v>425</v>
       </c>
       <c r="C411" t="s">
         <v>5</v>
@@ -6375,10 +6426,10 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B412" t="s">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="C412" t="s">
         <v>5</v>
@@ -6386,10 +6437,10 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B413" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C413" t="s">
         <v>5</v>
@@ -6397,10 +6448,10 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B414" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="C414" t="s">
         <v>5</v>
@@ -6408,10 +6459,10 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
+        <v>467</v>
+      </c>
+      <c r="B415" t="s">
         <v>468</v>
-      </c>
-      <c r="B415" t="s">
-        <v>362</v>
       </c>
       <c r="C415" t="s">
         <v>5</v>
@@ -6422,7 +6473,7 @@
         <v>469</v>
       </c>
       <c r="B416" t="s">
-        <v>449</v>
+        <v>377</v>
       </c>
       <c r="C416" t="s">
         <v>5</v>
@@ -6433,7 +6484,7 @@
         <v>470</v>
       </c>
       <c r="B417" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -6444,7 +6495,7 @@
         <v>471</v>
       </c>
       <c r="B418" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C418" t="s">
         <v>5</v>
@@ -6455,7 +6506,7 @@
         <v>472</v>
       </c>
       <c r="B419" t="s">
-        <v>358</v>
+        <v>107</v>
       </c>
       <c r="C419" t="s">
         <v>5</v>
@@ -6466,7 +6517,7 @@
         <v>473</v>
       </c>
       <c r="B420" t="s">
-        <v>364</v>
+        <v>112</v>
       </c>
       <c r="C420" t="s">
         <v>5</v>
@@ -6477,7 +6528,7 @@
         <v>474</v>
       </c>
       <c r="B421" t="s">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="C421" t="s">
         <v>5</v>
@@ -6488,7 +6539,7 @@
         <v>475</v>
       </c>
       <c r="B422" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="C422" t="s">
         <v>5</v>
@@ -6499,7 +6550,7 @@
         <v>476</v>
       </c>
       <c r="B423" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="C423" t="s">
         <v>5</v>
@@ -6510,7 +6561,7 @@
         <v>477</v>
       </c>
       <c r="B424" t="s">
-        <v>362</v>
+        <v>468</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
@@ -6521,7 +6572,7 @@
         <v>478</v>
       </c>
       <c r="B425" t="s">
-        <v>449</v>
+        <v>381</v>
       </c>
       <c r="C425" t="s">
         <v>5</v>
@@ -6532,7 +6583,7 @@
         <v>479</v>
       </c>
       <c r="B426" t="s">
-        <v>451</v>
+        <v>381</v>
       </c>
       <c r="C426" t="s">
         <v>5</v>
@@ -6543,7 +6594,7 @@
         <v>480</v>
       </c>
       <c r="B427" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C427" t="s">
         <v>5</v>
@@ -6554,7 +6605,7 @@
         <v>481</v>
       </c>
       <c r="B428" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C428" t="s">
         <v>5</v>
@@ -6565,7 +6616,7 @@
         <v>482</v>
       </c>
       <c r="B429" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C429" t="s">
         <v>5</v>
@@ -6576,7 +6627,7 @@
         <v>483</v>
       </c>
       <c r="B430" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C430" t="s">
         <v>5</v>
@@ -6587,7 +6638,7 @@
         <v>484</v>
       </c>
       <c r="B431" t="s">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
@@ -6598,7 +6649,7 @@
         <v>485</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="C432" t="s">
         <v>5</v>
@@ -6609,7 +6660,7 @@
         <v>486</v>
       </c>
       <c r="B433" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="C433" t="s">
         <v>5</v>
@@ -6620,7 +6671,7 @@
         <v>487</v>
       </c>
       <c r="B434" t="s">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
@@ -6631,7 +6682,7 @@
         <v>488</v>
       </c>
       <c r="B435" t="s">
-        <v>376</v>
+        <v>103</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
@@ -6642,7 +6693,7 @@
         <v>489</v>
       </c>
       <c r="B436" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C436" t="s">
         <v>5</v>
@@ -6653,7 +6704,7 @@
         <v>490</v>
       </c>
       <c r="B437" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C437" t="s">
         <v>5</v>
@@ -6664,7 +6715,7 @@
         <v>491</v>
       </c>
       <c r="B438" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C438" t="s">
         <v>5</v>
@@ -6675,7 +6726,7 @@
         <v>492</v>
       </c>
       <c r="B439" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C439" t="s">
         <v>5</v>
@@ -6686,7 +6737,7 @@
         <v>493</v>
       </c>
       <c r="B440" t="s">
-        <v>362</v>
+        <v>466</v>
       </c>
       <c r="C440" t="s">
         <v>5</v>
@@ -6697,7 +6748,7 @@
         <v>494</v>
       </c>
       <c r="B441" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C441" t="s">
         <v>5</v>
@@ -6708,7 +6759,7 @@
         <v>495</v>
       </c>
       <c r="B442" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="C442" t="s">
         <v>5</v>
@@ -6719,7 +6770,7 @@
         <v>496</v>
       </c>
       <c r="B443" t="s">
-        <v>364</v>
+        <v>468</v>
       </c>
       <c r="C443" t="s">
         <v>5</v>
@@ -6730,7 +6781,7 @@
         <v>497</v>
       </c>
       <c r="B444" t="s">
-        <v>449</v>
+        <v>379</v>
       </c>
       <c r="C444" t="s">
         <v>5</v>
@@ -6741,7 +6792,7 @@
         <v>498</v>
       </c>
       <c r="B445" t="s">
-        <v>432</v>
+        <v>383</v>
       </c>
       <c r="C445" t="s">
         <v>5</v>
@@ -6752,7 +6803,7 @@
         <v>499</v>
       </c>
       <c r="B446" t="s">
-        <v>432</v>
+        <v>383</v>
       </c>
       <c r="C446" t="s">
         <v>5</v>
@@ -6763,7 +6814,7 @@
         <v>500</v>
       </c>
       <c r="B447" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="C447" t="s">
         <v>5</v>
@@ -6774,7 +6825,7 @@
         <v>501</v>
       </c>
       <c r="B448" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="C448" t="s">
         <v>5</v>
@@ -6785,7 +6836,7 @@
         <v>502</v>
       </c>
       <c r="B449" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="C449" t="s">
         <v>5</v>
@@ -6796,9 +6847,196 @@
         <v>503</v>
       </c>
       <c r="B450" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="C450" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>504</v>
+      </c>
+      <c r="B451" t="s">
+        <v>449</v>
+      </c>
+      <c r="C451" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>505</v>
+      </c>
+      <c r="B452" t="s">
+        <v>393</v>
+      </c>
+      <c r="C452" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>506</v>
+      </c>
+      <c r="B453" t="s">
+        <v>383</v>
+      </c>
+      <c r="C453" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>507</v>
+      </c>
+      <c r="B454" t="s">
+        <v>379</v>
+      </c>
+      <c r="C454" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>508</v>
+      </c>
+      <c r="B455" t="s">
+        <v>381</v>
+      </c>
+      <c r="C455" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>509</v>
+      </c>
+      <c r="B456" t="s">
+        <v>379</v>
+      </c>
+      <c r="C456" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>510</v>
+      </c>
+      <c r="B457" t="s">
+        <v>379</v>
+      </c>
+      <c r="C457" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>511</v>
+      </c>
+      <c r="B458" t="s">
+        <v>383</v>
+      </c>
+      <c r="C458" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>512</v>
+      </c>
+      <c r="B459" t="s">
+        <v>381</v>
+      </c>
+      <c r="C459" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>513</v>
+      </c>
+      <c r="B460" t="s">
+        <v>381</v>
+      </c>
+      <c r="C460" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>514</v>
+      </c>
+      <c r="B461" t="s">
+        <v>466</v>
+      </c>
+      <c r="C461" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>515</v>
+      </c>
+      <c r="B462" t="s">
+        <v>449</v>
+      </c>
+      <c r="C462" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>516</v>
+      </c>
+      <c r="B463" t="s">
+        <v>449</v>
+      </c>
+      <c r="C463" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>517</v>
+      </c>
+      <c r="B464" t="s">
+        <v>423</v>
+      </c>
+      <c r="C464" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>518</v>
+      </c>
+      <c r="B465" t="s">
+        <v>423</v>
+      </c>
+      <c r="C465" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>519</v>
+      </c>
+      <c r="B466" t="s">
+        <v>423</v>
+      </c>
+      <c r="C466" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>520</v>
+      </c>
+      <c r="B467" t="s">
+        <v>423</v>
+      </c>
+      <c r="C467" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/GreatLink/Multi-Sector Income.xlsx
+++ b/data/GreatLink/Multi-Sector Income.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid222591"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid686424"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,162 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>0.904</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>0.905</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>0.897</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>0.898</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>0.899</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>0.896</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>0.891</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>0.893</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>0.900</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>0.894</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>0.902</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>0.903</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>0.907</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>0.909</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>0.914</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>0.913</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>0.912</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>0.915</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>0.918</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>0.917</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>0.921</t>
+  </si>
+  <si>
     <t>27/02/2026</t>
   </si>
   <si>
     <t>0.930</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>26/02/2026</t>
   </si>
   <si>
@@ -101,9 +248,6 @@
     <t>04/02/2026</t>
   </si>
   <si>
-    <t>0.921</t>
-  </si>
-  <si>
     <t>03/02/2026</t>
   </si>
   <si>
@@ -569,9 +713,6 @@
     <t>15/07/2025</t>
   </si>
   <si>
-    <t>0.918</t>
-  </si>
-  <si>
     <t>14/07/2025</t>
   </si>
   <si>
@@ -650,15 +791,9 @@
     <t>09/06/2025</t>
   </si>
   <si>
-    <t>0.917</t>
-  </si>
-  <si>
     <t>06/06/2025</t>
   </si>
   <si>
-    <t>0.915</t>
-  </si>
-  <si>
     <t>05/06/2025</t>
   </si>
   <si>
@@ -698,15 +833,9 @@
     <t>22/05/2025</t>
   </si>
   <si>
-    <t>0.913</t>
-  </si>
-  <si>
     <t>21/05/2025</t>
   </si>
   <si>
-    <t>0.912</t>
-  </si>
-  <si>
     <t>20/05/2025</t>
   </si>
   <si>
@@ -765,9 +894,6 @@
   </si>
   <si>
     <t>21/04/2025</t>
-  </si>
-  <si>
-    <t>0.914</t>
   </si>
   <si>
     <t>17/04/2025</t>
@@ -1930,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -1938,10 +2064,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -1949,10 +2075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -1960,10 +2086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1971,10 +2097,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -1982,10 +2108,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -1993,10 +2119,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -2004,10 +2130,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -2015,10 +2141,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -2026,10 +2152,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -2037,10 +2163,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -2048,10 +2174,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -2059,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2070,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -2081,10 +2207,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -2092,10 +2218,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -2103,10 +2229,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -2114,10 +2240,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -2125,10 +2251,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -2136,10 +2262,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -2147,10 +2273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -2158,10 +2284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -2169,10 +2295,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -2180,10 +2306,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -2191,10 +2317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -2202,10 +2328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -2213,10 +2339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -2224,10 +2350,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -2235,10 +2361,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -2246,10 +2372,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -2257,10 +2383,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -2268,10 +2394,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -2279,10 +2405,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -2290,10 +2416,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -2301,10 +2427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -2312,10 +2438,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -2323,10 +2449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -2334,10 +2460,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -2345,10 +2471,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -2356,10 +2482,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -2367,10 +2493,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -2378,10 +2504,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -2389,10 +2515,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -2400,10 +2526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -2411,10 +2537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -2422,10 +2548,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -2433,10 +2559,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -2444,10 +2570,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" t="s">
         <v>62</v>
-      </c>
-      <c r="B50" t="s">
-        <v>13</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -2455,10 +2581,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -2466,10 +2592,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -2477,10 +2603,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -2488,10 +2614,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -2499,10 +2625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -2510,10 +2636,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -2521,10 +2647,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -2532,10 +2658,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -2543,10 +2669,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -2554,10 +2680,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -2565,10 +2691,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -2576,10 +2702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -2587,10 +2713,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -2598,10 +2724,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -2609,10 +2735,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -2620,10 +2746,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -2631,10 +2757,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -2642,10 +2768,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -2653,10 +2779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -2664,10 +2790,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -2675,10 +2801,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -2686,10 +2812,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -2697,10 +2823,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -2708,10 +2834,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -2719,7 +2845,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
         <v>80</v>
@@ -2730,10 +2856,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -2741,10 +2867,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -2752,10 +2878,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -2763,10 +2889,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -2774,10 +2900,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -2785,10 +2911,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -2796,10 +2922,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B82" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -2807,10 +2933,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B83" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -2818,10 +2944,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -2829,10 +2955,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -2840,10 +2966,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -2851,10 +2977,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B87" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -2862,10 +2988,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B88" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -2873,10 +2999,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B89" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -2884,10 +3010,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B90" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -2895,10 +3021,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -2906,10 +3032,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B92" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -2917,10 +3043,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B93" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -2928,10 +3054,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
@@ -2939,10 +3065,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
@@ -2950,10 +3076,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
@@ -2961,10 +3087,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
@@ -2972,10 +3098,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C98" t="s">
         <v>5</v>
@@ -2983,10 +3109,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
@@ -2994,10 +3120,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -3005,10 +3131,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C101" t="s">
         <v>5</v>
@@ -3016,10 +3142,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
@@ -3027,10 +3153,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="C103" t="s">
         <v>5</v>
@@ -3038,10 +3164,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -3049,10 +3175,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -3060,10 +3186,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C106" t="s">
         <v>5</v>
@@ -3071,10 +3197,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B107" t="s">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
@@ -3082,10 +3208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B108" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="C108" t="s">
         <v>5</v>
@@ -3093,10 +3219,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>144</v>
+      </c>
+      <c r="B109" t="s">
         <v>130</v>
-      </c>
-      <c r="B109" t="s">
-        <v>80</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -3104,10 +3230,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C110" t="s">
         <v>5</v>
@@ -3115,10 +3241,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -3126,10 +3252,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B112" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C112" t="s">
         <v>5</v>
@@ -3137,10 +3263,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="B113" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="C113" t="s">
         <v>5</v>
@@ -3148,10 +3274,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C114" t="s">
         <v>5</v>
@@ -3159,10 +3285,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B115" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C115" t="s">
         <v>5</v>
@@ -3170,10 +3296,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B116" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C116" t="s">
         <v>5</v>
@@ -3181,10 +3307,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B117" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
@@ -3192,10 +3318,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B118" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="C118" t="s">
         <v>5</v>
@@ -3203,10 +3329,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B119" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
@@ -3214,10 +3340,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
@@ -3225,10 +3351,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
@@ -3236,10 +3362,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B122" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3247,10 +3373,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B123" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="C123" t="s">
         <v>5</v>
@@ -3258,10 +3384,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -3269,10 +3395,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="B125" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C125" t="s">
         <v>5</v>
@@ -3280,10 +3406,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
@@ -3291,10 +3417,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="B127" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
@@ -3302,10 +3428,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="B128" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C128" t="s">
         <v>5</v>
@@ -3313,10 +3439,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B129" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
@@ -3324,10 +3450,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="B130" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C130" t="s">
         <v>5</v>
@@ -3335,10 +3461,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B131" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="C131" t="s">
         <v>5</v>
@@ -3346,10 +3472,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C132" t="s">
         <v>5</v>
@@ -3357,10 +3483,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B133" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -3368,10 +3494,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
@@ -3379,10 +3505,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
@@ -3390,10 +3516,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B136" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -3401,10 +3527,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
@@ -3412,10 +3538,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B138" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
@@ -3423,10 +3549,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B139" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
@@ -3434,10 +3560,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
@@ -3445,10 +3571,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B141" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
@@ -3456,10 +3582,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B142" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -3467,10 +3593,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -3478,10 +3604,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -3489,10 +3615,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -3500,10 +3626,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
@@ -3511,10 +3637,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
@@ -3522,10 +3648,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B148" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
@@ -3533,10 +3659,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B149" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
@@ -3544,10 +3670,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="B150" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
@@ -3555,10 +3681,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B151" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
@@ -3566,10 +3692,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B152" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C152" t="s">
         <v>5</v>
@@ -3577,10 +3703,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B153" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C153" t="s">
         <v>5</v>
@@ -3588,10 +3714,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B154" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C154" t="s">
         <v>5</v>
@@ -3599,10 +3725,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B155" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -3610,10 +3736,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B156" t="s">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="C156" t="s">
         <v>5</v>
@@ -3621,10 +3747,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B157" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C157" t="s">
         <v>5</v>
@@ -3632,10 +3758,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B158" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -3643,10 +3769,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B159" t="s">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
@@ -3654,10 +3780,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B160" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
@@ -3665,10 +3791,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B161" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
@@ -3676,10 +3802,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B162" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C162" t="s">
         <v>5</v>
@@ -3687,10 +3813,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B163" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="C163" t="s">
         <v>5</v>
@@ -3698,10 +3824,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B164" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="C164" t="s">
         <v>5</v>
@@ -3709,10 +3835,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B165" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C165" t="s">
         <v>5</v>
@@ -3720,10 +3846,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C166" t="s">
         <v>5</v>
@@ -3731,10 +3857,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B167" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
@@ -3742,10 +3868,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B168" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -3753,10 +3879,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B169" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -3764,10 +3890,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B170" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -3775,10 +3901,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B171" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -3786,10 +3912,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B172" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
@@ -3797,10 +3923,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B173" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -3808,10 +3934,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B174" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -3819,10 +3945,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B175" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
@@ -3830,10 +3956,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B176" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -3841,10 +3967,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B177" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
@@ -3852,10 +3978,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B178" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
@@ -3863,10 +3989,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B179" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
@@ -3874,10 +4000,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B180" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
@@ -3885,10 +4011,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B181" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -3896,10 +4022,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C182" t="s">
         <v>5</v>
@@ -3907,10 +4033,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C183" t="s">
         <v>5</v>
@@ -3918,10 +4044,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B184" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="C184" t="s">
         <v>5</v>
@@ -3929,10 +4055,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B185" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="C185" t="s">
         <v>5</v>
@@ -3940,10 +4066,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B186" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -3951,10 +4077,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B187" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
@@ -3962,10 +4088,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B188" t="s">
-        <v>215</v>
+        <v>48</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -3973,10 +4099,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B189" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
@@ -3984,10 +4110,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B190" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -3995,10 +4121,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B191" t="s">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -4006,10 +4132,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="B192" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -4017,10 +4143,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B193" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -4028,10 +4154,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B194" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -4039,10 +4165,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B195" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -4050,10 +4176,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B196" t="s">
-        <v>213</v>
+        <v>69</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -4061,10 +4187,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B197" t="s">
-        <v>213</v>
+        <v>69</v>
       </c>
       <c r="C197" t="s">
         <v>5</v>
@@ -4072,10 +4198,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B198" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
@@ -4083,10 +4209,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B199" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
@@ -4094,10 +4220,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B200" t="s">
-        <v>211</v>
+        <v>54</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
@@ -4105,10 +4231,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B201" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
@@ -4116,10 +4242,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B202" t="s">
-        <v>184</v>
+        <v>62</v>
       </c>
       <c r="C202" t="s">
         <v>5</v>
@@ -4127,10 +4253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B203" t="s">
-        <v>211</v>
+        <v>62</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -4138,10 +4264,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B204" t="s">
-        <v>227</v>
+        <v>71</v>
       </c>
       <c r="C204" t="s">
         <v>5</v>
@@ -4149,10 +4275,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B205" t="s">
-        <v>219</v>
+        <v>75</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -4160,10 +4286,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B206" t="s">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
@@ -4171,10 +4297,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B207" t="s">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -4182,10 +4308,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B208" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
@@ -4193,10 +4319,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B209" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
@@ -4204,10 +4330,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B210" t="s">
-        <v>219</v>
+        <v>52</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
@@ -4215,10 +4341,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B211" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -4226,10 +4352,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B212" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -4237,10 +4363,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B213" t="s">
-        <v>8</v>
+        <v>229</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -4248,10 +4374,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
@@ -4259,10 +4385,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B215" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
@@ -4270,10 +4396,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B216" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
@@ -4281,10 +4407,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B217" t="s">
-        <v>215</v>
+        <v>52</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -4292,10 +4418,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B218" t="s">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="C218" t="s">
         <v>5</v>
@@ -4303,10 +4429,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B219" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -4314,10 +4440,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B220" t="s">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="C220" t="s">
         <v>5</v>
@@ -4325,10 +4451,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B221" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -4336,10 +4462,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B222" t="s">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="C222" t="s">
         <v>5</v>
@@ -4347,10 +4473,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B223" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="C223" t="s">
         <v>5</v>
@@ -4358,10 +4484,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B224" t="s">
-        <v>256</v>
+        <v>46</v>
       </c>
       <c r="C224" t="s">
         <v>5</v>
@@ -4369,10 +4495,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B225" t="s">
-        <v>258</v>
+        <v>46</v>
       </c>
       <c r="C225" t="s">
         <v>5</v>
@@ -4380,10 +4506,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B226" t="s">
-        <v>213</v>
+        <v>42</v>
       </c>
       <c r="C226" t="s">
         <v>5</v>
@@ -4391,10 +4517,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B227" t="s">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="C227" t="s">
         <v>5</v>
@@ -4402,10 +4528,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B228" t="s">
-        <v>215</v>
+        <v>50</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -4413,10 +4539,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B229" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -4424,10 +4550,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B230" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -4435,10 +4561,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B231" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="C231" t="s">
         <v>5</v>
@@ -4446,10 +4572,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B232" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="C232" t="s">
         <v>5</v>
@@ -4457,10 +4583,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B233" t="s">
-        <v>112</v>
+        <v>264</v>
       </c>
       <c r="C233" t="s">
         <v>5</v>
@@ -4468,10 +4594,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B234" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C234" t="s">
         <v>5</v>
@@ -4479,10 +4605,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B235" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C235" t="s">
         <v>5</v>
@@ -4490,10 +4616,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B236" t="s">
-        <v>112</v>
+        <v>229</v>
       </c>
       <c r="C236" t="s">
         <v>5</v>
@@ -4501,10 +4627,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B237" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C237" t="s">
         <v>5</v>
@@ -4512,10 +4638,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B238" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
@@ -4523,10 +4649,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -4534,10 +4660,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B240" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -4545,10 +4671,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B241" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="C241" t="s">
         <v>5</v>
@@ -4556,10 +4682,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B242" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C242" t="s">
         <v>5</v>
@@ -4567,10 +4693,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B243" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="C243" t="s">
         <v>5</v>
@@ -4578,10 +4704,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B244" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
@@ -4589,10 +4715,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B245" t="s">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="C245" t="s">
         <v>5</v>
@@ -4600,10 +4726,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B246" t="s">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="C246" t="s">
         <v>5</v>
@@ -4611,10 +4737,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B247" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="C247" t="s">
         <v>5</v>
@@ -4622,10 +4748,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B248" t="s">
-        <v>112</v>
+        <v>260</v>
       </c>
       <c r="C248" t="s">
         <v>5</v>
@@ -4633,10 +4759,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B249" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
@@ -4644,10 +4770,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B250" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
@@ -4655,10 +4781,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B251" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="C251" t="s">
         <v>5</v>
@@ -4666,10 +4792,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B252" t="s">
-        <v>137</v>
+        <v>298</v>
       </c>
       <c r="C252" t="s">
         <v>5</v>
@@ -4677,10 +4803,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B253" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
@@ -4688,10 +4814,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B254" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="C254" t="s">
         <v>5</v>
@@ -4699,10 +4825,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B255" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="C255" t="s">
         <v>5</v>
@@ -4710,10 +4836,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B256" t="s">
-        <v>105</v>
+        <v>260</v>
       </c>
       <c r="C256" t="s">
         <v>5</v>
@@ -4721,10 +4847,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B257" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -4732,10 +4858,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B258" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
@@ -4743,10 +4869,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B259" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="C259" t="s">
         <v>5</v>
@@ -4754,10 +4880,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B260" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="C260" t="s">
         <v>5</v>
@@ -4765,10 +4891,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B261" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="C261" t="s">
         <v>5</v>
@@ -4776,10 +4902,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B262" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
@@ -4787,10 +4913,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B263" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C263" t="s">
         <v>5</v>
@@ -4798,10 +4924,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B264" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
@@ -4809,10 +4935,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B265" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="C265" t="s">
         <v>5</v>
@@ -4820,10 +4946,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B266" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="C266" t="s">
         <v>5</v>
@@ -4831,10 +4957,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B267" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="C267" t="s">
         <v>5</v>
@@ -4842,10 +4968,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B268" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="C268" t="s">
         <v>5</v>
@@ -4853,10 +4979,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B269" t="s">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
@@ -4864,10 +4990,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B270" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="C270" t="s">
         <v>5</v>
@@ -4875,10 +5001,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="C271" t="s">
         <v>5</v>
@@ -4886,10 +5012,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B272" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -4897,10 +5023,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B273" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="C273" t="s">
         <v>5</v>
@@ -4908,10 +5034,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B274" t="s">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -4919,10 +5045,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B275" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -4930,10 +5056,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B276" t="s">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -4941,10 +5067,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B277" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -4952,10 +5078,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B278" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -4963,10 +5089,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B279" t="s">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="C279" t="s">
         <v>5</v>
@@ -4974,10 +5100,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B280" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -4985,10 +5111,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B281" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="C281" t="s">
         <v>5</v>
@@ -4996,10 +5122,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B282" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="C282" t="s">
         <v>5</v>
@@ -5007,10 +5133,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B283" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="C283" t="s">
         <v>5</v>
@@ -5018,10 +5144,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B284" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="C284" t="s">
         <v>5</v>
@@ -5029,10 +5155,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B285" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="C285" t="s">
         <v>5</v>
@@ -5040,10 +5166,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B286" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="C286" t="s">
         <v>5</v>
@@ -5051,10 +5177,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B287" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="C287" t="s">
         <v>5</v>
@@ -5062,10 +5188,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B288" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="C288" t="s">
         <v>5</v>
@@ -5073,10 +5199,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B289" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="C289" t="s">
         <v>5</v>
@@ -5084,10 +5210,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B290" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -5095,10 +5221,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="C291" t="s">
         <v>5</v>
@@ -5106,10 +5232,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B292" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="C292" t="s">
         <v>5</v>
@@ -5117,10 +5243,10 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B293" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C293" t="s">
         <v>5</v>
@@ -5128,10 +5254,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B294" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C294" t="s">
         <v>5</v>
@@ -5139,10 +5265,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B295" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="C295" t="s">
         <v>5</v>
@@ -5150,10 +5276,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B296" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="C296" t="s">
         <v>5</v>
@@ -5161,10 +5287,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B297" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="C297" t="s">
         <v>5</v>
@@ -5172,10 +5298,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B298" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="C298" t="s">
         <v>5</v>
@@ -5183,10 +5309,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B299" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -5194,10 +5320,10 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B300" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C300" t="s">
         <v>5</v>
@@ -5205,10 +5331,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B301" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C301" t="s">
         <v>5</v>
@@ -5216,10 +5342,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B302" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C302" t="s">
         <v>5</v>
@@ -5227,10 +5353,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B303" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C303" t="s">
         <v>5</v>
@@ -5238,7 +5364,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B304" t="s">
         <v>80</v>
@@ -5249,10 +5375,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B305" t="s">
-        <v>137</v>
+        <v>67</v>
       </c>
       <c r="C305" t="s">
         <v>5</v>
@@ -5260,10 +5386,10 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B306" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="C306" t="s">
         <v>5</v>
@@ -5271,10 +5397,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B307" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="C307" t="s">
         <v>5</v>
@@ -5282,10 +5408,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B308" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C308" t="s">
         <v>5</v>
@@ -5293,10 +5419,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B309" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="C309" t="s">
         <v>5</v>
@@ -5304,10 +5430,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B310" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C310" t="s">
         <v>5</v>
@@ -5315,10 +5441,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B311" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="C311" t="s">
         <v>5</v>
@@ -5326,10 +5452,10 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B312" t="s">
-        <v>101</v>
+        <v>264</v>
       </c>
       <c r="C312" t="s">
         <v>5</v>
@@ -5337,10 +5463,10 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B313" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="C313" t="s">
         <v>5</v>
@@ -5348,10 +5474,10 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B314" t="s">
-        <v>101</v>
+        <v>264</v>
       </c>
       <c r="C314" t="s">
         <v>5</v>
@@ -5359,10 +5485,10 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B315" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C315" t="s">
         <v>5</v>
@@ -5370,10 +5496,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B316" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C316" t="s">
         <v>5</v>
@@ -5381,10 +5507,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B317" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="C317" t="s">
         <v>5</v>
@@ -5392,10 +5518,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B318" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C318" t="s">
         <v>5</v>
@@ -5403,10 +5529,10 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B319" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C319" t="s">
         <v>5</v>
@@ -5414,10 +5540,10 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B320" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C320" t="s">
         <v>5</v>
@@ -5425,10 +5551,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B321" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C321" t="s">
         <v>5</v>
@@ -5436,10 +5562,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B322" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C322" t="s">
         <v>5</v>
@@ -5447,10 +5573,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B323" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C323" t="s">
         <v>5</v>
@@ -5458,10 +5584,10 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B324" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C324" t="s">
         <v>5</v>
@@ -5469,10 +5595,10 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B325" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C325" t="s">
         <v>5</v>
@@ -5480,10 +5606,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B326" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C326" t="s">
         <v>5</v>
@@ -5491,10 +5617,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B327" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C327" t="s">
         <v>5</v>
@@ -5502,10 +5628,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B328" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C328" t="s">
         <v>5</v>
@@ -5513,10 +5639,10 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B329" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="C329" t="s">
         <v>5</v>
@@ -5524,10 +5650,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B330" t="s">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="C330" t="s">
         <v>5</v>
@@ -5535,10 +5661,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B331" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="C331" t="s">
         <v>5</v>
@@ -5546,10 +5672,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B332" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="C332" t="s">
         <v>5</v>
@@ -5557,10 +5683,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B333" t="s">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="C333" t="s">
         <v>5</v>
@@ -5568,10 +5694,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B334" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="C334" t="s">
         <v>5</v>
@@ -5579,10 +5705,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B335" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C335" t="s">
         <v>5</v>
@@ -5590,10 +5716,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B336" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="C336" t="s">
         <v>5</v>
@@ -5601,10 +5727,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B337" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="C337" t="s">
         <v>5</v>
@@ -5612,10 +5738,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B338" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="C338" t="s">
         <v>5</v>
@@ -5623,10 +5749,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B339" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="C339" t="s">
         <v>5</v>
@@ -5634,10 +5760,10 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B340" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="C340" t="s">
         <v>5</v>
@@ -5645,10 +5771,10 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B341" t="s">
-        <v>375</v>
+        <v>155</v>
       </c>
       <c r="C341" t="s">
         <v>5</v>
@@ -5656,10 +5782,10 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B342" t="s">
-        <v>377</v>
+        <v>149</v>
       </c>
       <c r="C342" t="s">
         <v>5</v>
@@ -5667,10 +5793,10 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B343" t="s">
-        <v>379</v>
+        <v>153</v>
       </c>
       <c r="C343" t="s">
         <v>5</v>
@@ -5678,10 +5804,10 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B344" t="s">
-        <v>381</v>
+        <v>153</v>
       </c>
       <c r="C344" t="s">
         <v>5</v>
@@ -5689,10 +5815,10 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B345" t="s">
-        <v>383</v>
+        <v>155</v>
       </c>
       <c r="C345" t="s">
         <v>5</v>
@@ -5700,10 +5826,10 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B346" t="s">
-        <v>379</v>
+        <v>155</v>
       </c>
       <c r="C346" t="s">
         <v>5</v>
@@ -5711,10 +5837,10 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B347" t="s">
-        <v>381</v>
+        <v>128</v>
       </c>
       <c r="C347" t="s">
         <v>5</v>
@@ -5722,10 +5848,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B348" t="s">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="C348" t="s">
         <v>5</v>
@@ -5733,10 +5859,10 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B349" t="s">
-        <v>381</v>
+        <v>164</v>
       </c>
       <c r="C349" t="s">
         <v>5</v>
@@ -5744,10 +5870,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B350" t="s">
-        <v>381</v>
+        <v>128</v>
       </c>
       <c r="C350" t="s">
         <v>5</v>
@@ -5755,10 +5881,10 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B351" t="s">
-        <v>381</v>
+        <v>128</v>
       </c>
       <c r="C351" t="s">
         <v>5</v>
@@ -5766,10 +5892,10 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B352" t="s">
-        <v>381</v>
+        <v>164</v>
       </c>
       <c r="C352" t="s">
         <v>5</v>
@@ -5777,10 +5903,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B353" t="s">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="C353" t="s">
         <v>5</v>
@@ -5788,10 +5914,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B354" t="s">
-        <v>393</v>
+        <v>164</v>
       </c>
       <c r="C354" t="s">
         <v>5</v>
@@ -5799,10 +5925,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B355" t="s">
-        <v>395</v>
+        <v>164</v>
       </c>
       <c r="C355" t="s">
         <v>5</v>
@@ -5810,10 +5936,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="B356" t="s">
-        <v>395</v>
+        <v>149</v>
       </c>
       <c r="C356" t="s">
         <v>5</v>
@@ -5821,10 +5947,10 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B357" t="s">
-        <v>398</v>
+        <v>155</v>
       </c>
       <c r="C357" t="s">
         <v>5</v>
@@ -5832,10 +5958,10 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B358" t="s">
-        <v>400</v>
+        <v>149</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -5843,10 +5969,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B359" t="s">
-        <v>402</v>
+        <v>130</v>
       </c>
       <c r="C359" t="s">
         <v>5</v>
@@ -5854,10 +5980,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B360" t="s">
-        <v>398</v>
+        <v>130</v>
       </c>
       <c r="C360" t="s">
         <v>5</v>
@@ -5865,10 +5991,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B361" t="s">
-        <v>405</v>
+        <v>54</v>
       </c>
       <c r="C361" t="s">
         <v>5</v>
@@ -5876,10 +6002,10 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B362" t="s">
-        <v>400</v>
+        <v>128</v>
       </c>
       <c r="C362" t="s">
         <v>5</v>
@@ -5887,10 +6013,10 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B363" t="s">
-        <v>405</v>
+        <v>185</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
@@ -5898,10 +6024,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B364" t="s">
-        <v>405</v>
+        <v>155</v>
       </c>
       <c r="C364" t="s">
         <v>5</v>
@@ -5909,10 +6035,10 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B365" t="s">
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="C365" t="s">
         <v>5</v>
@@ -5920,10 +6046,10 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B366" t="s">
-        <v>400</v>
+        <v>153</v>
       </c>
       <c r="C366" t="s">
         <v>5</v>
@@ -5931,10 +6057,10 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B367" t="s">
-        <v>400</v>
+        <v>153</v>
       </c>
       <c r="C367" t="s">
         <v>5</v>
@@ -5942,10 +6068,10 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B368" t="s">
-        <v>398</v>
+        <v>155</v>
       </c>
       <c r="C368" t="s">
         <v>5</v>
@@ -5953,10 +6079,10 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B369" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C369" t="s">
         <v>5</v>
@@ -5964,10 +6090,10 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B370" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C370" t="s">
         <v>5</v>
@@ -5975,10 +6101,10 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C371" t="s">
         <v>5</v>
@@ -5986,10 +6112,10 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B372" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="C372" t="s">
         <v>5</v>
@@ -5997,10 +6123,10 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B373" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C373" t="s">
         <v>5</v>
@@ -6008,10 +6134,10 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
+        <v>426</v>
+      </c>
+      <c r="B374" t="s">
         <v>421</v>
-      </c>
-      <c r="B374" t="s">
-        <v>393</v>
       </c>
       <c r="C374" t="s">
         <v>5</v>
@@ -6019,7 +6145,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B375" t="s">
         <v>423</v>
@@ -6030,10 +6156,10 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B376" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C376" t="s">
         <v>5</v>
@@ -6041,10 +6167,10 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B377" t="s">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="C377" t="s">
         <v>5</v>
@@ -6052,10 +6178,10 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B378" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C378" t="s">
         <v>5</v>
@@ -6063,10 +6189,10 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B379" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="C379" t="s">
         <v>5</v>
@@ -6074,10 +6200,10 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B380" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C380" t="s">
         <v>5</v>
@@ -6085,10 +6211,10 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B381" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C381" t="s">
         <v>5</v>
@@ -6096,10 +6222,10 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B382" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C382" t="s">
         <v>5</v>
@@ -6107,10 +6233,10 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B383" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C383" t="s">
         <v>5</v>
@@ -6118,10 +6244,10 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B384" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="C384" t="s">
         <v>5</v>
@@ -6129,10 +6255,10 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B385" t="s">
-        <v>395</v>
+        <v>440</v>
       </c>
       <c r="C385" t="s">
         <v>5</v>
@@ -6140,10 +6266,10 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B386" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
@@ -6151,10 +6277,10 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B387" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="C387" t="s">
         <v>5</v>
@@ -6162,10 +6288,10 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B388" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C388" t="s">
         <v>5</v>
@@ -6173,10 +6299,10 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B389" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C389" t="s">
         <v>5</v>
@@ -6184,10 +6310,10 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B390" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
@@ -6195,10 +6321,10 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B391" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C391" t="s">
         <v>5</v>
@@ -6206,10 +6332,10 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B392" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="C392" t="s">
         <v>5</v>
@@ -6217,10 +6343,10 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B393" t="s">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="C393" t="s">
         <v>5</v>
@@ -6228,10 +6354,10 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B394" t="s">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="C394" t="s">
         <v>5</v>
@@ -6239,10 +6365,10 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B395" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="C395" t="s">
         <v>5</v>
@@ -6250,10 +6376,10 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B396" t="s">
-        <v>379</v>
+        <v>440</v>
       </c>
       <c r="C396" t="s">
         <v>5</v>
@@ -6261,10 +6387,10 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B397" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="C397" t="s">
         <v>5</v>
@@ -6272,10 +6398,10 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="B398" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C398" t="s">
         <v>5</v>
@@ -6283,10 +6409,10 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B399" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="C399" t="s">
         <v>5</v>
@@ -6294,10 +6420,10 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B400" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C400" t="s">
         <v>5</v>
@@ -6305,10 +6431,10 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B401" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="C401" t="s">
         <v>5</v>
@@ -6316,10 +6442,10 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B402" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="C402" t="s">
         <v>5</v>
@@ -6327,10 +6453,10 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="B403" t="s">
-        <v>383</v>
+        <v>465</v>
       </c>
       <c r="C403" t="s">
         <v>5</v>
@@ -6338,10 +6464,10 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B404" t="s">
-        <v>379</v>
+        <v>467</v>
       </c>
       <c r="C404" t="s">
         <v>5</v>
@@ -6349,10 +6475,10 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B405" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="C405" t="s">
         <v>5</v>
@@ -6360,10 +6486,10 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B406" t="s">
-        <v>383</v>
+        <v>462</v>
       </c>
       <c r="C406" t="s">
         <v>5</v>
@@ -6371,10 +6497,10 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B407" t="s">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="C407" t="s">
         <v>5</v>
@@ -6382,10 +6508,10 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="B408" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="C408" t="s">
         <v>5</v>
@@ -6393,10 +6519,10 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B409" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="C409" t="s">
         <v>5</v>
@@ -6404,10 +6530,10 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="B410" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C410" t="s">
         <v>5</v>
@@ -6415,10 +6541,10 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="B411" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="C411" t="s">
         <v>5</v>
@@ -6426,10 +6552,10 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="B412" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="C412" t="s">
         <v>5</v>
@@ -6437,10 +6563,10 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B413" t="s">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="C413" t="s">
         <v>5</v>
@@ -6448,10 +6574,10 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B414" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C414" t="s">
         <v>5</v>
@@ -6459,10 +6585,10 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B415" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C415" t="s">
         <v>5</v>
@@ -6470,10 +6596,10 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B416" t="s">
-        <v>377</v>
+        <v>462</v>
       </c>
       <c r="C416" t="s">
         <v>5</v>
@@ -6481,10 +6607,10 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B417" t="s">
-        <v>375</v>
+        <v>465</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -6492,10 +6618,10 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B418" t="s">
-        <v>107</v>
+        <v>435</v>
       </c>
       <c r="C418" t="s">
         <v>5</v>
@@ -6503,10 +6629,10 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B419" t="s">
-        <v>107</v>
+        <v>465</v>
       </c>
       <c r="C419" t="s">
         <v>5</v>
@@ -6514,10 +6640,10 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B420" t="s">
-        <v>112</v>
+        <v>467</v>
       </c>
       <c r="C420" t="s">
         <v>5</v>
@@ -6525,10 +6651,10 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B421" t="s">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="C421" t="s">
         <v>5</v>
@@ -6536,10 +6662,10 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B422" t="s">
-        <v>377</v>
+        <v>423</v>
       </c>
       <c r="C422" t="s">
         <v>5</v>
@@ -6547,10 +6673,10 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B423" t="s">
-        <v>468</v>
+        <v>421</v>
       </c>
       <c r="C423" t="s">
         <v>5</v>
@@ -6558,10 +6684,10 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B424" t="s">
-        <v>468</v>
+        <v>421</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
@@ -6569,10 +6695,10 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B425" t="s">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="C425" t="s">
         <v>5</v>
@@ -6580,10 +6706,10 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B426" t="s">
-        <v>381</v>
+        <v>491</v>
       </c>
       <c r="C426" t="s">
         <v>5</v>
@@ -6591,10 +6717,10 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B427" t="s">
-        <v>381</v>
+        <v>437</v>
       </c>
       <c r="C427" t="s">
         <v>5</v>
@@ -6602,10 +6728,10 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B428" t="s">
-        <v>381</v>
+        <v>491</v>
       </c>
       <c r="C428" t="s">
         <v>5</v>
@@ -6613,10 +6739,10 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B429" t="s">
-        <v>381</v>
+        <v>491</v>
       </c>
       <c r="C429" t="s">
         <v>5</v>
@@ -6624,10 +6750,10 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B430" t="s">
-        <v>381</v>
+        <v>491</v>
       </c>
       <c r="C430" t="s">
         <v>5</v>
@@ -6635,10 +6761,10 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B431" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
@@ -6646,10 +6772,10 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B432" t="s">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="C432" t="s">
         <v>5</v>
@@ -6657,10 +6783,10 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B433" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="C433" t="s">
         <v>5</v>
@@ -6668,10 +6794,10 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B434" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
@@ -6679,10 +6805,10 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B435" t="s">
-        <v>103</v>
+        <v>425</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
@@ -6690,10 +6816,10 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B436" t="s">
-        <v>375</v>
+        <v>467</v>
       </c>
       <c r="C436" t="s">
         <v>5</v>
@@ -6701,10 +6827,10 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B437" t="s">
-        <v>381</v>
+        <v>491</v>
       </c>
       <c r="C437" t="s">
         <v>5</v>
@@ -6712,10 +6838,10 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
+        <v>503</v>
+      </c>
+      <c r="B438" t="s">
         <v>491</v>
-      </c>
-      <c r="B438" t="s">
-        <v>379</v>
       </c>
       <c r="C438" t="s">
         <v>5</v>
@@ -6723,10 +6849,10 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B439" t="s">
-        <v>381</v>
+        <v>467</v>
       </c>
       <c r="C439" t="s">
         <v>5</v>
@@ -6734,10 +6860,10 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B440" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="C440" t="s">
         <v>5</v>
@@ -6745,10 +6871,10 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B441" t="s">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="C441" t="s">
         <v>5</v>
@@ -6756,10 +6882,10 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B442" t="s">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="C442" t="s">
         <v>5</v>
@@ -6767,10 +6893,10 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="B443" t="s">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="C443" t="s">
         <v>5</v>
@@ -6778,10 +6904,10 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="B444" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="C444" t="s">
         <v>5</v>
@@ -6789,10 +6915,10 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="B445" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C445" t="s">
         <v>5</v>
@@ -6800,10 +6926,10 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="B446" t="s">
-        <v>383</v>
+        <v>155</v>
       </c>
       <c r="C446" t="s">
         <v>5</v>
@@ -6811,10 +6937,10 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="B447" t="s">
-        <v>379</v>
+        <v>155</v>
       </c>
       <c r="C447" t="s">
         <v>5</v>
@@ -6822,10 +6948,10 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="B448" t="s">
-        <v>423</v>
+        <v>160</v>
       </c>
       <c r="C448" t="s">
         <v>5</v>
@@ -6833,10 +6959,10 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="B449" t="s">
-        <v>449</v>
+        <v>125</v>
       </c>
       <c r="C449" t="s">
         <v>5</v>
@@ -6844,10 +6970,10 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="B450" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="C450" t="s">
         <v>5</v>
@@ -6855,10 +6981,10 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>510</v>
       </c>
       <c r="C451" t="s">
         <v>5</v>
@@ -6866,10 +6992,10 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="B452" t="s">
-        <v>393</v>
+        <v>510</v>
       </c>
       <c r="C452" t="s">
         <v>5</v>
@@ -6877,10 +7003,10 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="B453" t="s">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="C453" t="s">
         <v>5</v>
@@ -6888,10 +7014,10 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B454" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="C454" t="s">
         <v>5</v>
@@ -6899,10 +7025,10 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="B455" t="s">
-        <v>381</v>
+        <v>423</v>
       </c>
       <c r="C455" t="s">
         <v>5</v>
@@ -6910,10 +7036,10 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="B456" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="C456" t="s">
         <v>5</v>
@@ -6921,10 +7047,10 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="B457" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="C457" t="s">
         <v>5</v>
@@ -6932,10 +7058,10 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="B458" t="s">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="C458" t="s">
         <v>5</v>
@@ -6943,10 +7069,10 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="B459" t="s">
-        <v>381</v>
+        <v>508</v>
       </c>
       <c r="C459" t="s">
         <v>5</v>
@@ -6954,10 +7080,10 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="B460" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="C460" t="s">
         <v>5</v>
@@ -6965,10 +7091,10 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="B461" t="s">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="C461" t="s">
         <v>5</v>
@@ -6976,10 +7102,10 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="B462" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="C462" t="s">
         <v>5</v>
@@ -6987,10 +7113,10 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="B463" t="s">
-        <v>449</v>
+        <v>151</v>
       </c>
       <c r="C463" t="s">
         <v>5</v>
@@ -6998,10 +7124,10 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="B464" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C464" t="s">
         <v>5</v>
@@ -7009,7 +7135,7 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="B465" t="s">
         <v>423</v>
@@ -7020,10 +7146,10 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="B466" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C466" t="s">
         <v>5</v>
@@ -7031,12 +7157,320 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="B467" t="s">
         <v>423</v>
       </c>
       <c r="C467" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>535</v>
+      </c>
+      <c r="B468" t="s">
+        <v>508</v>
+      </c>
+      <c r="C468" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>536</v>
+      </c>
+      <c r="B469" t="s">
+        <v>421</v>
+      </c>
+      <c r="C469" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>537</v>
+      </c>
+      <c r="B470" t="s">
+        <v>508</v>
+      </c>
+      <c r="C470" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>538</v>
+      </c>
+      <c r="B471" t="s">
+        <v>510</v>
+      </c>
+      <c r="C471" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>539</v>
+      </c>
+      <c r="B472" t="s">
+        <v>421</v>
+      </c>
+      <c r="C472" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>540</v>
+      </c>
+      <c r="B473" t="s">
+        <v>425</v>
+      </c>
+      <c r="C473" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>541</v>
+      </c>
+      <c r="B474" t="s">
+        <v>425</v>
+      </c>
+      <c r="C474" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>542</v>
+      </c>
+      <c r="B475" t="s">
+        <v>421</v>
+      </c>
+      <c r="C475" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>543</v>
+      </c>
+      <c r="B476" t="s">
+        <v>465</v>
+      </c>
+      <c r="C476" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>544</v>
+      </c>
+      <c r="B477" t="s">
+        <v>491</v>
+      </c>
+      <c r="C477" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>545</v>
+      </c>
+      <c r="B478" t="s">
+        <v>491</v>
+      </c>
+      <c r="C478" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>546</v>
+      </c>
+      <c r="B479" t="s">
+        <v>491</v>
+      </c>
+      <c r="C479" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>547</v>
+      </c>
+      <c r="B480" t="s">
+        <v>435</v>
+      </c>
+      <c r="C480" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>548</v>
+      </c>
+      <c r="B481" t="s">
+        <v>425</v>
+      </c>
+      <c r="C481" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>549</v>
+      </c>
+      <c r="B482" t="s">
+        <v>421</v>
+      </c>
+      <c r="C482" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>550</v>
+      </c>
+      <c r="B483" t="s">
+        <v>423</v>
+      </c>
+      <c r="C483" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>551</v>
+      </c>
+      <c r="B484" t="s">
+        <v>421</v>
+      </c>
+      <c r="C484" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>552</v>
+      </c>
+      <c r="B485" t="s">
+        <v>421</v>
+      </c>
+      <c r="C485" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>553</v>
+      </c>
+      <c r="B486" t="s">
+        <v>425</v>
+      </c>
+      <c r="C486" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>554</v>
+      </c>
+      <c r="B487" t="s">
+        <v>423</v>
+      </c>
+      <c r="C487" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>555</v>
+      </c>
+      <c r="B488" t="s">
+        <v>423</v>
+      </c>
+      <c r="C488" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>556</v>
+      </c>
+      <c r="B489" t="s">
+        <v>508</v>
+      </c>
+      <c r="C489" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>557</v>
+      </c>
+      <c r="B490" t="s">
+        <v>491</v>
+      </c>
+      <c r="C490" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="s">
+        <v>558</v>
+      </c>
+      <c r="B491" t="s">
+        <v>491</v>
+      </c>
+      <c r="C491" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="s">
+        <v>559</v>
+      </c>
+      <c r="B492" t="s">
+        <v>465</v>
+      </c>
+      <c r="C492" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="s">
+        <v>560</v>
+      </c>
+      <c r="B493" t="s">
+        <v>465</v>
+      </c>
+      <c r="C493" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="s">
+        <v>561</v>
+      </c>
+      <c r="B494" t="s">
+        <v>465</v>
+      </c>
+      <c r="C494" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s">
+        <v>562</v>
+      </c>
+      <c r="B495" t="s">
+        <v>465</v>
+      </c>
+      <c r="C495" t="s">
         <v>5</v>
       </c>
     </row>
